--- a/esyluban/examples/release/DataTables/demo.xlsx
+++ b/esyluban/examples/release/DataTables/demo.xlsx
@@ -1617,9 +1617,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="G1:I1"/>
     <mergeCell ref="G2:I2"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="G3:I3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2115,16 +2115,16 @@
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="K1:O1"/>
-    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="K3:O3"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="T5:V5"/>
+    <mergeCell ref="M4:O4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="F2:J2"/>
     <mergeCell ref="K2:O2"/>
-    <mergeCell ref="T4:V4"/>
-    <mergeCell ref="R3:V3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="F1:J1"/>
-    <mergeCell ref="P1:V1"/>
-    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="P3:V3"/>
+    <mergeCell ref="R4:V4"/>
     <mergeCell ref="P2:V2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2503,15 +2503,15 @@
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="R3:U3"/>
     <mergeCell ref="R2:U2"/>
-    <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="R1:U1"/>
-    <mergeCell ref="F1:J1"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:N3"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="C3:E3"/>
     <mergeCell ref="K2:N2"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="H3:J3"/>
     <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="O3:Q3"/>
     <mergeCell ref="F2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2685,7 +2685,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="C2:F2"/>
-    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="C3:F3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2818,9 +2818,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="C3:F3"/>
     <mergeCell ref="C2:F2"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="D4:F4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3013,7 +3013,7 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C4:E4"/>
     <mergeCell ref="C3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3367,13 +3367,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="I1:L1"/>
-    <mergeCell ref="M1:P1"/>
-    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="M3:P3"/>
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="C3:E3"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="M2:P2"/>
     <mergeCell ref="I2:L2"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3668,11 +3668,11 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="G3:K3"/>
     <mergeCell ref="L2:P2"/>
-    <mergeCell ref="L1:P1"/>
+    <mergeCell ref="L3:P3"/>
+    <mergeCell ref="C3:F3"/>
     <mergeCell ref="G2:K2"/>
-    <mergeCell ref="G1:K1"/>
-    <mergeCell ref="C1:F1"/>
     <mergeCell ref="C2:F2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5094,8 +5094,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="F3:I3"/>
     <mergeCell ref="F2:I2"/>
-    <mergeCell ref="F1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5462,12 +5462,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="H3:K3"/>
+    <mergeCell ref="L3:O3"/>
     <mergeCell ref="H2:K2"/>
     <mergeCell ref="L2:O2"/>
-    <mergeCell ref="D1:G1"/>
     <mergeCell ref="D2:G2"/>
-    <mergeCell ref="H1:K1"/>
-    <mergeCell ref="L1:O1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5831,12 +5831,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="H3:K3"/>
+    <mergeCell ref="L3:O3"/>
     <mergeCell ref="H2:K2"/>
     <mergeCell ref="L2:O2"/>
-    <mergeCell ref="D1:G1"/>
     <mergeCell ref="D2:G2"/>
-    <mergeCell ref="H1:K1"/>
-    <mergeCell ref="L1:O1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6819,10 +6819,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="Q1:S1"/>
-    <mergeCell ref="M1:P1"/>
-    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="M2:P2"/>
+    <mergeCell ref="Q3:S3"/>
     <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="M3:O3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7090,8 +7090,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="E3:H3"/>
     <mergeCell ref="E2:H2"/>
-    <mergeCell ref="E1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7238,7 +7238,7 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C4:E4"/>
     <mergeCell ref="C3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7378,9 +7378,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C3:F3"/>
     <mergeCell ref="C2:F2"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7652,14 +7652,14 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="I2:K2"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="L3:O3"/>
+    <mergeCell ref="C4:E4"/>
     <mergeCell ref="L2:O2"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="F2:H2"/>
-    <mergeCell ref="L1:O1"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
